--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -6061,7 +6061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -6209,6 +6209,28 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pago inicial al aceptar (%)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Número de cuenta (IBAN)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ESXX XXXX XXXX XXXX XXXX XXXX</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/catalogo.xlsx
+++ b/catalogo.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tableros" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acabados" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extras" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herrajes" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Piezas" sheetId="10" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medidas" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recargo" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parámetros" sheetId="8" state="visible" r:id="rId8"/>
@@ -450,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -552,7 +554,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>• Canto = Canto (se cobra canto por los lados marcados), Pulido (se cobra canteado de todo el perímetro, sin material de canto) o No.</t>
+          <t>• Canto = Canto (se cobra el canto y el canteado de los lados marcados), Pulido (los lados marcados se pulen: se cobra el canteado, sin material de canto) o No.</t>
         </is>
       </c>
     </row>
@@ -579,6 +581,257 @@
           <t>Si quieres pasarlos a precios nuevos, ábrelos y pulsa «Actualizar a precios actuales».</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Herrajes y extras:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>• «Herrajes»: bisagras, cajones, colgadores… La columna Categoría agrupa los modelos (en la app se elige primero la categoría y luego el modelo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>• «Extras»: el resto de accesorios y trabajos que se cobran por unidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Lijado (pestaña «Familias»):</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>• Columna «Lijado (€/m² por cara)»: solo para materiales que se lijan antes de barnizar (Rechapado). Se cobra por las caras con acabado (1 o 2), junto al acabado opcional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Piezas:</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>• Nombres de pieza habituales que salen en el desplegable de la app, con sus cantos (L1 = canto delantero). Al elegir uno se marcan sus cantos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>• El generador de muebles usa estos mismos nombres (Lateral, Sobre, Base, Estante fijo, Estante móvil, Divisoria, Frontal…).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Cantos (L1 L2 A1 A2 / Todos / vacío)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lateral</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lateral visto</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sobre</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Estante fijo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Divisoria</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Estante móvil</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Frontal</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Puerta</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Frente de cajón</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Zócalo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Trasera</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Regleta vertical</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Regleta horizontal</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -591,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -599,6 +852,7 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,6 +881,11 @@
           <t>Medida tablero por defecto (cm)</t>
         </is>
       </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Lijado (€/m² por cara)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -707,6 +966,9 @@
         <is>
           <t>244x122</t>
         </is>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4640,102 +4902,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bissagra Amortiguada</t>
+          <t>Escambell Calaixos</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>2.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nivellador base</t>
+          <t>Fressat Unyero</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1.45</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Barra Penjador</t>
+          <t>Fressat LED</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Suport barra</t>
+          <t>Base Armari</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.27</v>
+        <v>20.49</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Calaix guia Emuca</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>52.51</v>
-      </c>
+      <c r="B6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Calaix guia Blum</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>81.94</v>
-      </c>
+      <c r="B7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Escambell Calaixos</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>50</v>
-      </c>
+      <c r="B8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fressat Unyero</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>11.66</v>
-      </c>
+      <c r="B9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fressat LED</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>5</v>
-      </c>
+      <c r="B10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Base Armari</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>20.49</v>
-      </c>
+      <c r="B11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="4" t="n"/>
@@ -6061,7 +6281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6179,7 +6399,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -6209,6 +6429,763 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pago inicial al aceptar (%)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Número de cuenta (IBAN)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ESXX XXXX XXXX XXXX XXXX XXXX</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C210"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Precio (€/ud)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bisagras</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bissagra Amortiguada</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cajones</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Calaix guia Emuca</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>52.51</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cajones</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Calaix guia Blum</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>81.94</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Colgadores</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Barra Penjador</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Colgadores</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Suport barra</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Niveladores</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nivellador base</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="C32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="C40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="C41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="C43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="C44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="C46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="C48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="C50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="C51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="C55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="C60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="C61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="C62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="C63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="C64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="C65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="C66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="C67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="C68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="C69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="C70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="C71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="C72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="C73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="C74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="C75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="C76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="C77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="C78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="C79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="C80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="C81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="C82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="C83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="C84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="C85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="C86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="C87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="C88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="C89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="C90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="C91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="C92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="C93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="C94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="C95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="C96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="C97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="C98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="C99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="C100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="C101" s="4" t="n"/>
+    </row>
+    <row r="102">
+      <c r="C102" s="4" t="n"/>
+    </row>
+    <row r="103">
+      <c r="C103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="C104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="C105" s="4" t="n"/>
+    </row>
+    <row r="106">
+      <c r="C106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="C107" s="4" t="n"/>
+    </row>
+    <row r="108">
+      <c r="C108" s="4" t="n"/>
+    </row>
+    <row r="109">
+      <c r="C109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="C110" s="4" t="n"/>
+    </row>
+    <row r="111">
+      <c r="C111" s="4" t="n"/>
+    </row>
+    <row r="112">
+      <c r="C112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="C113" s="4" t="n"/>
+    </row>
+    <row r="114">
+      <c r="C114" s="4" t="n"/>
+    </row>
+    <row r="115">
+      <c r="C115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="C116" s="4" t="n"/>
+    </row>
+    <row r="117">
+      <c r="C117" s="4" t="n"/>
+    </row>
+    <row r="118">
+      <c r="C118" s="4" t="n"/>
+    </row>
+    <row r="119">
+      <c r="C119" s="4" t="n"/>
+    </row>
+    <row r="120">
+      <c r="C120" s="4" t="n"/>
+    </row>
+    <row r="121">
+      <c r="C121" s="4" t="n"/>
+    </row>
+    <row r="122">
+      <c r="C122" s="4" t="n"/>
+    </row>
+    <row r="123">
+      <c r="C123" s="4" t="n"/>
+    </row>
+    <row r="124">
+      <c r="C124" s="4" t="n"/>
+    </row>
+    <row r="125">
+      <c r="C125" s="4" t="n"/>
+    </row>
+    <row r="126">
+      <c r="C126" s="4" t="n"/>
+    </row>
+    <row r="127">
+      <c r="C127" s="4" t="n"/>
+    </row>
+    <row r="128">
+      <c r="C128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="C129" s="4" t="n"/>
+    </row>
+    <row r="130">
+      <c r="C130" s="4" t="n"/>
+    </row>
+    <row r="131">
+      <c r="C131" s="4" t="n"/>
+    </row>
+    <row r="132">
+      <c r="C132" s="4" t="n"/>
+    </row>
+    <row r="133">
+      <c r="C133" s="4" t="n"/>
+    </row>
+    <row r="134">
+      <c r="C134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="C135" s="4" t="n"/>
+    </row>
+    <row r="136">
+      <c r="C136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="C137" s="4" t="n"/>
+    </row>
+    <row r="138">
+      <c r="C138" s="4" t="n"/>
+    </row>
+    <row r="139">
+      <c r="C139" s="4" t="n"/>
+    </row>
+    <row r="140">
+      <c r="C140" s="4" t="n"/>
+    </row>
+    <row r="141">
+      <c r="C141" s="4" t="n"/>
+    </row>
+    <row r="142">
+      <c r="C142" s="4" t="n"/>
+    </row>
+    <row r="143">
+      <c r="C143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="C144" s="4" t="n"/>
+    </row>
+    <row r="145">
+      <c r="C145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="C146" s="4" t="n"/>
+    </row>
+    <row r="147">
+      <c r="C147" s="4" t="n"/>
+    </row>
+    <row r="148">
+      <c r="C148" s="4" t="n"/>
+    </row>
+    <row r="149">
+      <c r="C149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="C150" s="4" t="n"/>
+    </row>
+    <row r="151">
+      <c r="C151" s="4" t="n"/>
+    </row>
+    <row r="152">
+      <c r="C152" s="4" t="n"/>
+    </row>
+    <row r="153">
+      <c r="C153" s="4" t="n"/>
+    </row>
+    <row r="154">
+      <c r="C154" s="4" t="n"/>
+    </row>
+    <row r="155">
+      <c r="C155" s="4" t="n"/>
+    </row>
+    <row r="156">
+      <c r="C156" s="4" t="n"/>
+    </row>
+    <row r="157">
+      <c r="C157" s="4" t="n"/>
+    </row>
+    <row r="158">
+      <c r="C158" s="4" t="n"/>
+    </row>
+    <row r="159">
+      <c r="C159" s="4" t="n"/>
+    </row>
+    <row r="160">
+      <c r="C160" s="4" t="n"/>
+    </row>
+    <row r="161">
+      <c r="C161" s="4" t="n"/>
+    </row>
+    <row r="162">
+      <c r="C162" s="4" t="n"/>
+    </row>
+    <row r="163">
+      <c r="C163" s="4" t="n"/>
+    </row>
+    <row r="164">
+      <c r="C164" s="4" t="n"/>
+    </row>
+    <row r="165">
+      <c r="C165" s="4" t="n"/>
+    </row>
+    <row r="166">
+      <c r="C166" s="4" t="n"/>
+    </row>
+    <row r="167">
+      <c r="C167" s="4" t="n"/>
+    </row>
+    <row r="168">
+      <c r="C168" s="4" t="n"/>
+    </row>
+    <row r="169">
+      <c r="C169" s="4" t="n"/>
+    </row>
+    <row r="170">
+      <c r="C170" s="4" t="n"/>
+    </row>
+    <row r="171">
+      <c r="C171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="C172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="C173" s="4" t="n"/>
+    </row>
+    <row r="174">
+      <c r="C174" s="4" t="n"/>
+    </row>
+    <row r="175">
+      <c r="C175" s="4" t="n"/>
+    </row>
+    <row r="176">
+      <c r="C176" s="4" t="n"/>
+    </row>
+    <row r="177">
+      <c r="C177" s="4" t="n"/>
+    </row>
+    <row r="178">
+      <c r="C178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="C179" s="4" t="n"/>
+    </row>
+    <row r="180">
+      <c r="C180" s="4" t="n"/>
+    </row>
+    <row r="181">
+      <c r="C181" s="4" t="n"/>
+    </row>
+    <row r="182">
+      <c r="C182" s="4" t="n"/>
+    </row>
+    <row r="183">
+      <c r="C183" s="4" t="n"/>
+    </row>
+    <row r="184">
+      <c r="C184" s="4" t="n"/>
+    </row>
+    <row r="185">
+      <c r="C185" s="4" t="n"/>
+    </row>
+    <row r="186">
+      <c r="C186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="C187" s="4" t="n"/>
+    </row>
+    <row r="188">
+      <c r="C188" s="4" t="n"/>
+    </row>
+    <row r="189">
+      <c r="C189" s="4" t="n"/>
+    </row>
+    <row r="190">
+      <c r="C190" s="4" t="n"/>
+    </row>
+    <row r="191">
+      <c r="C191" s="4" t="n"/>
+    </row>
+    <row r="192">
+      <c r="C192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="C193" s="4" t="n"/>
+    </row>
+    <row r="194">
+      <c r="C194" s="4" t="n"/>
+    </row>
+    <row r="195">
+      <c r="C195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="C196" s="4" t="n"/>
+    </row>
+    <row r="197">
+      <c r="C197" s="4" t="n"/>
+    </row>
+    <row r="198">
+      <c r="C198" s="4" t="n"/>
+    </row>
+    <row r="199">
+      <c r="C199" s="4" t="n"/>
+    </row>
+    <row r="200">
+      <c r="C200" s="4" t="n"/>
+    </row>
+    <row r="201">
+      <c r="C201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="C202" s="4" t="n"/>
+    </row>
+    <row r="203">
+      <c r="C203" s="4" t="n"/>
+    </row>
+    <row r="204">
+      <c r="C204" s="4" t="n"/>
+    </row>
+    <row r="205">
+      <c r="C205" s="4" t="n"/>
+    </row>
+    <row r="206">
+      <c r="C206" s="4" t="n"/>
+    </row>
+    <row r="207">
+      <c r="C207" s="4" t="n"/>
+    </row>
+    <row r="208">
+      <c r="C208" s="4" t="n"/>
+    </row>
+    <row r="209">
+      <c r="C209" s="4" t="n"/>
+    </row>
+    <row r="210">
+      <c r="C210" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
